--- a/cds_files/Louisville_CDS_2024-2025.xlsx
+++ b/cds_files/Louisville_CDS_2024-2025.xlsx
@@ -427,6 +427,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -434,9 +435,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12297</v>
-      </c>
-    </row>
+        <v>17086</v>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -489,6 +491,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -522,7 +525,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.238</v>
+        <v>0.289</v>
       </c>
       <c r="C5" t="n">
         <v>0.238</v>
@@ -607,7 +610,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
